--- a/nr-update-missing-fields/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/nr-update-missing-fields/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T07:52:36+00:00</t>
+    <t>2024-07-17T09:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-missing-fields/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/nr-update-missing-fields/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T09:13:15+00:00</t>
+    <t>2024-07-17T12:12:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-missing-fields/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/nr-update-missing-fields/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:12:47+00:00</t>
+    <t>2024-07-17T15:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-missing-fields/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/nr-update-missing-fields/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:12:21+00:00</t>
+    <t>2024-07-25T07:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
